--- a/data/reports/dedicated_competitors_20260817.xlsx
+++ b/data/reports/dedicated_competitors_20260817.xlsx
@@ -2930,7 +2930,7 @@
         <v>100</v>
       </c>
       <c r="M47" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N47" t="n">
         <v>2</v>
@@ -3372,10 +3372,10 @@
         <v>100</v>
       </c>
       <c r="M54" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
@@ -10630,13 +10630,33 @@
       <c r="G193" t="n">
         <v>59780</v>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+      <c r="H193" t="n">
+        <v>121240</v>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>PCL07-NVMe</t>
+        </is>
+      </c>
+      <c r="L193" t="n">
+        <v>100</v>
+      </c>
+      <c r="M193" t="n">
+        <v>4</v>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
